--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>아이디</t>
   </si>
@@ -121,9 +121,6 @@
     <t>pet_skill_fire_001</t>
   </si>
   <si>
-    <t>pet_passive_burn</t>
-  </si>
-  <si>
     <t>pet_water_002</t>
   </si>
   <si>
@@ -200,7 +197,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +208,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
       </patternFill>
     </fill>
   </fills>
@@ -234,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -252,6 +255,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,9 +631,7 @@
       <c r="F4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="G4" s="6"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -648,25 +652,25 @@
     </row>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -688,22 +692,22 @@
     </row>
     <row r="6" ht="31.5" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -726,22 +730,22 @@
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>

--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26205" windowHeight="12135"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
-  <si>
-    <t>아이디</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>이름</t>
   </si>
@@ -30,20 +35,24 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1100.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">엑티브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1000.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -51,20 +60,24 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1100.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">패시브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1000.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -103,9 +116,6 @@
     <t>IconPath</t>
   </si>
   <si>
-    <t>pet_fire_001</t>
-  </si>
-  <si>
     <t>플레임폰</t>
   </si>
   <si>
@@ -119,9 +129,6 @@
   </si>
   <si>
     <t>pet_skill_fire_001</t>
-  </si>
-  <si>
-    <t>pet_water_002</t>
   </si>
   <si>
     <t>워터폰</t>
@@ -139,9 +146,6 @@
     <t>pet_passive_water_regeneration</t>
   </si>
   <si>
-    <t>pet_earth_003</t>
-  </si>
-  <si>
     <t>어스폰</t>
   </si>
   <si>
@@ -152,9 +156,6 @@
   </si>
   <si>
     <t>pet_skill_earth_001,pet_skill_taunt</t>
-  </si>
-  <si>
-    <t>pet_air_004</t>
   </si>
   <si>
     <t>윈드폰</t>
@@ -168,33 +169,91 @@
   <si>
     <t>pet_skill_air_001,pet_skill_windblessing</t>
   </si>
+  <si>
+    <t>아이디</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet_Fire_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Pet_Fire_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet_Water_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Pet_Water_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet_Earth_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Pet_Earth_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet_Air_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/Pet_Air_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="409.55"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -202,7 +261,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -218,7 +277,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -232,43 +297,47 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -276,7 +345,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -466,50 +535,51 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.5"/>
-    <col customWidth="1" min="2" max="2" width="7.75"/>
-    <col customWidth="1" min="3" max="3" width="15.25"/>
-    <col customWidth="1" min="4" max="4" width="56.0"/>
-    <col customWidth="1" min="5" max="5" width="16.0"/>
-    <col customWidth="1" min="6" max="6" width="28.0"/>
-    <col customWidth="1" min="7" max="7" width="27.63"/>
-    <col customWidth="1" min="8" max="24" width="13.0"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="7.75" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="56" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="54.5" customWidth="1"/>
+    <col min="7" max="7" width="44.875" customWidth="1"/>
+    <col min="8" max="8" width="53.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="24" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:24" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -528,30 +598,30 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" ht="24.0" customHeight="1">
+    <row r="2" spans="1:24" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -570,30 +640,30 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" ht="27.75" customHeight="1">
+    <row r="3" spans="1:24" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -612,27 +682,29 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
+    <row r="4" spans="1:24" ht="31.5" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
+      <c r="G4" s="6"/>
+      <c r="H4" s="4" t="s">
+        <v>37</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -650,29 +722,31 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
+    <row r="5" spans="1:24" ht="31.5" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
+      <c r="H5" s="4" t="s">
+        <v>39</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -690,27 +764,29 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1">
+    <row r="6" spans="1:24" ht="31.5" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>31</v>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>41</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -728,27 +804,29 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1">
+    <row r="7" spans="1:24" ht="31.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -766,7 +844,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:24" ht="13.5">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -792,7 +870,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:24" ht="13.5">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -818,7 +896,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:24" ht="13.5">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -844,7 +922,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:24" ht="13.5">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -870,7 +948,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:24" ht="13.5">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -896,7 +974,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:24" ht="13.5">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -922,7 +1000,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:24" ht="13.5">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -947,7 +1025,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:24" ht="13.5">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -973,7 +1051,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:24" ht="13.5">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -999,7 +1077,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:24" ht="13.5">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1025,7 +1103,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:24" ht="13.5">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1051,7 +1129,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:24" ht="13.5">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1077,7 +1155,7 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:24" ht="13.5">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1103,7 +1181,7 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:24" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1129,7 +1207,7 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:24" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1155,7 +1233,7 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:24" ht="15.75" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1181,7 +1259,7 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:24" ht="15.75" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1207,7 +1285,7 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:24" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1233,7 +1311,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:24" ht="15.75" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1259,7 +1337,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:24" ht="15.75" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1285,7 +1363,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:24" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1311,7 +1389,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:24" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1337,7 +1415,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:24" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1363,7 +1441,7 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:24" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1389,7 +1467,7 @@
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:24" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1415,7 +1493,7 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:24" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1441,7 +1519,7 @@
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:24" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1467,7 +1545,7 @@
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:24" ht="15.75" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1493,7 +1571,7 @@
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:24" ht="15.75" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1519,7 +1597,7 @@
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:24" ht="15.75" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1545,7 +1623,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:24" ht="15.75" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1571,7 +1649,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:24" ht="15.75" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1597,7 +1675,7 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:24" ht="15.75" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1623,7 +1701,7 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:24" ht="15.75" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1649,7 +1727,7 @@
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:24" ht="15.75" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1675,7 +1753,7 @@
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:24" ht="15.75" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1701,7 +1779,7 @@
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:24" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1727,7 +1805,7 @@
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:24" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1753,7 +1831,7 @@
       <c r="W45" s="5"/>
       <c r="X45" s="5"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:24" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1779,7 +1857,7 @@
       <c r="W46" s="5"/>
       <c r="X46" s="5"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:24" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1805,7 +1883,7 @@
       <c r="W47" s="5"/>
       <c r="X47" s="5"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:24" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1831,7 +1909,7 @@
       <c r="W48" s="5"/>
       <c r="X48" s="5"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:24" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1857,7 +1935,7 @@
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:24" ht="15.75" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1883,7 +1961,7 @@
       <c r="W50" s="5"/>
       <c r="X50" s="5"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:24" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1909,7 +1987,7 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:24" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -1935,7 +2013,7 @@
       <c r="W52" s="5"/>
       <c r="X52" s="5"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:24" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1961,7 +2039,7 @@
       <c r="W53" s="5"/>
       <c r="X53" s="5"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:24" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1987,7 +2065,7 @@
       <c r="W54" s="5"/>
       <c r="X54" s="5"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:24" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2013,7 +2091,7 @@
       <c r="W55" s="5"/>
       <c r="X55" s="5"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:24" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2039,7 +2117,7 @@
       <c r="W56" s="5"/>
       <c r="X56" s="5"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:24" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2065,7 +2143,7 @@
       <c r="W57" s="5"/>
       <c r="X57" s="5"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:24" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2091,7 +2169,7 @@
       <c r="W58" s="5"/>
       <c r="X58" s="5"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:24" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2117,7 +2195,7 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:24" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2143,7 +2221,7 @@
       <c r="W60" s="5"/>
       <c r="X60" s="5"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:24" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2169,7 +2247,7 @@
       <c r="W61" s="5"/>
       <c r="X61" s="5"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:24" ht="15.75" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2195,7 +2273,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:24" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2221,7 +2299,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:24" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2247,7 +2325,7 @@
       <c r="W64" s="5"/>
       <c r="X64" s="5"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:24" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2273,7 +2351,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:24" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2299,7 +2377,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:24" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2325,7 +2403,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:24" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2351,7 +2429,7 @@
       <c r="W68" s="5"/>
       <c r="X68" s="5"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:24" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2377,7 +2455,7 @@
       <c r="W69" s="5"/>
       <c r="X69" s="5"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:24" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2403,7 +2481,7 @@
       <c r="W70" s="5"/>
       <c r="X70" s="5"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:24" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2429,7 +2507,7 @@
       <c r="W71" s="5"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:24" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2455,7 +2533,7 @@
       <c r="W72" s="5"/>
       <c r="X72" s="5"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:24" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2481,7 +2559,7 @@
       <c r="W73" s="5"/>
       <c r="X73" s="5"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:24" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2507,7 +2585,7 @@
       <c r="W74" s="5"/>
       <c r="X74" s="5"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:24" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2533,7 +2611,7 @@
       <c r="W75" s="5"/>
       <c r="X75" s="5"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:24" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2559,7 +2637,7 @@
       <c r="W76" s="5"/>
       <c r="X76" s="5"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:24" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2585,7 +2663,7 @@
       <c r="W77" s="5"/>
       <c r="X77" s="5"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:24" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2611,7 +2689,7 @@
       <c r="W78" s="5"/>
       <c r="X78" s="5"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:24" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2637,7 +2715,7 @@
       <c r="W79" s="5"/>
       <c r="X79" s="5"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:24" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2663,7 +2741,7 @@
       <c r="W80" s="5"/>
       <c r="X80" s="5"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:24" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2689,7 +2767,7 @@
       <c r="W81" s="5"/>
       <c r="X81" s="5"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:24" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2715,7 +2793,7 @@
       <c r="W82" s="5"/>
       <c r="X82" s="5"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:24" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2741,7 +2819,7 @@
       <c r="W83" s="5"/>
       <c r="X83" s="5"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:24" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2767,7 +2845,7 @@
       <c r="W84" s="5"/>
       <c r="X84" s="5"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:24" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2793,7 +2871,7 @@
       <c r="W85" s="5"/>
       <c r="X85" s="5"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:24" ht="15.75" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2819,7 +2897,7 @@
       <c r="W86" s="5"/>
       <c r="X86" s="5"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:24" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2845,7 +2923,7 @@
       <c r="W87" s="5"/>
       <c r="X87" s="5"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:24" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2871,7 +2949,7 @@
       <c r="W88" s="5"/>
       <c r="X88" s="5"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:24" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2897,7 +2975,7 @@
       <c r="W89" s="5"/>
       <c r="X89" s="5"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:24" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2923,7 +3001,7 @@
       <c r="W90" s="5"/>
       <c r="X90" s="5"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:24" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2949,7 +3027,7 @@
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:24" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2975,7 +3053,7 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:24" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3001,7 +3079,7 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:24" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3027,7 +3105,7 @@
       <c r="W94" s="5"/>
       <c r="X94" s="5"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:24" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3053,7 +3131,7 @@
       <c r="W95" s="5"/>
       <c r="X95" s="5"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:24" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3079,7 +3157,7 @@
       <c r="W96" s="5"/>
       <c r="X96" s="5"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:24" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3105,7 +3183,7 @@
       <c r="W97" s="5"/>
       <c r="X97" s="5"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:24" ht="15.75" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3131,7 +3209,7 @@
       <c r="W98" s="5"/>
       <c r="X98" s="5"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:24" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3157,7 +3235,7 @@
       <c r="W99" s="5"/>
       <c r="X99" s="5"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:24" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3183,7 +3261,7 @@
       <c r="W100" s="5"/>
       <c r="X100" s="5"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:24" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3209,7 +3287,7 @@
       <c r="W101" s="5"/>
       <c r="X101" s="5"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:24" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3235,7 +3313,7 @@
       <c r="W102" s="5"/>
       <c r="X102" s="5"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:24" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3261,7 +3339,7 @@
       <c r="W103" s="5"/>
       <c r="X103" s="5"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:24" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3287,7 +3365,7 @@
       <c r="W104" s="5"/>
       <c r="X104" s="5"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:24" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3313,7 +3391,7 @@
       <c r="W105" s="5"/>
       <c r="X105" s="5"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:24" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3339,7 +3417,7 @@
       <c r="W106" s="5"/>
       <c r="X106" s="5"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:24" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3365,7 +3443,7 @@
       <c r="W107" s="5"/>
       <c r="X107" s="5"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:24" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3391,7 +3469,7 @@
       <c r="W108" s="5"/>
       <c r="X108" s="5"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:24" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3417,7 +3495,7 @@
       <c r="W109" s="5"/>
       <c r="X109" s="5"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:24" ht="15.75" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3443,7 +3521,7 @@
       <c r="W110" s="5"/>
       <c r="X110" s="5"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:24" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3469,7 +3547,7 @@
       <c r="W111" s="5"/>
       <c r="X111" s="5"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:24" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3495,7 +3573,7 @@
       <c r="W112" s="5"/>
       <c r="X112" s="5"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:24" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3521,7 +3599,7 @@
       <c r="W113" s="5"/>
       <c r="X113" s="5"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:24" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3547,7 +3625,7 @@
       <c r="W114" s="5"/>
       <c r="X114" s="5"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:24" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3573,7 +3651,7 @@
       <c r="W115" s="5"/>
       <c r="X115" s="5"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:24" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3599,7 +3677,7 @@
       <c r="W116" s="5"/>
       <c r="X116" s="5"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:24" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3625,7 +3703,7 @@
       <c r="W117" s="5"/>
       <c r="X117" s="5"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:24" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3651,7 +3729,7 @@
       <c r="W118" s="5"/>
       <c r="X118" s="5"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:24" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3677,7 +3755,7 @@
       <c r="W119" s="5"/>
       <c r="X119" s="5"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:24" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3703,7 +3781,7 @@
       <c r="W120" s="5"/>
       <c r="X120" s="5"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3729,7 +3807,7 @@
       <c r="W121" s="5"/>
       <c r="X121" s="5"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:24" ht="15.75" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3755,7 +3833,7 @@
       <c r="W122" s="5"/>
       <c r="X122" s="5"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3781,7 +3859,7 @@
       <c r="W123" s="5"/>
       <c r="X123" s="5"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:24" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3807,7 +3885,7 @@
       <c r="W124" s="5"/>
       <c r="X124" s="5"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:24" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3833,7 +3911,7 @@
       <c r="W125" s="5"/>
       <c r="X125" s="5"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:24" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3859,7 +3937,7 @@
       <c r="W126" s="5"/>
       <c r="X126" s="5"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:24" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3885,7 +3963,7 @@
       <c r="W127" s="5"/>
       <c r="X127" s="5"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:24" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3911,7 +3989,7 @@
       <c r="W128" s="5"/>
       <c r="X128" s="5"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:24" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3937,7 +4015,7 @@
       <c r="W129" s="5"/>
       <c r="X129" s="5"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:24" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3963,7 +4041,7 @@
       <c r="W130" s="5"/>
       <c r="X130" s="5"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:24" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3989,7 +4067,7 @@
       <c r="W131" s="5"/>
       <c r="X131" s="5"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:24" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4015,7 +4093,7 @@
       <c r="W132" s="5"/>
       <c r="X132" s="5"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4041,7 +4119,7 @@
       <c r="W133" s="5"/>
       <c r="X133" s="5"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:24" ht="15.75" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4067,7 +4145,7 @@
       <c r="W134" s="5"/>
       <c r="X134" s="5"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:24" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4093,7 +4171,7 @@
       <c r="W135" s="5"/>
       <c r="X135" s="5"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:24" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4119,7 +4197,7 @@
       <c r="W136" s="5"/>
       <c r="X136" s="5"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:24" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4145,7 +4223,7 @@
       <c r="W137" s="5"/>
       <c r="X137" s="5"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:24" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4171,7 +4249,7 @@
       <c r="W138" s="5"/>
       <c r="X138" s="5"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:24" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4197,7 +4275,7 @@
       <c r="W139" s="5"/>
       <c r="X139" s="5"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:24" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4223,7 +4301,7 @@
       <c r="W140" s="5"/>
       <c r="X140" s="5"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:24" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4249,7 +4327,7 @@
       <c r="W141" s="5"/>
       <c r="X141" s="5"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:24" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4275,7 +4353,7 @@
       <c r="W142" s="5"/>
       <c r="X142" s="5"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:24" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4301,7 +4379,7 @@
       <c r="W143" s="5"/>
       <c r="X143" s="5"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:24" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4327,7 +4405,7 @@
       <c r="W144" s="5"/>
       <c r="X144" s="5"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:24" ht="15.75" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4353,7 +4431,7 @@
       <c r="W145" s="5"/>
       <c r="X145" s="5"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:24" ht="15.75" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4379,7 +4457,7 @@
       <c r="W146" s="5"/>
       <c r="X146" s="5"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:24" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4405,7 +4483,7 @@
       <c r="W147" s="5"/>
       <c r="X147" s="5"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:24" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4431,7 +4509,7 @@
       <c r="W148" s="5"/>
       <c r="X148" s="5"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:24" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4457,7 +4535,7 @@
       <c r="W149" s="5"/>
       <c r="X149" s="5"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:24" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4483,7 +4561,7 @@
       <c r="W150" s="5"/>
       <c r="X150" s="5"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:24" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4509,7 +4587,7 @@
       <c r="W151" s="5"/>
       <c r="X151" s="5"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:24" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4535,7 +4613,7 @@
       <c r="W152" s="5"/>
       <c r="X152" s="5"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:24" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4561,7 +4639,7 @@
       <c r="W153" s="5"/>
       <c r="X153" s="5"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:24" ht="15.75" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4587,7 +4665,7 @@
       <c r="W154" s="5"/>
       <c r="X154" s="5"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:24" ht="15.75" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4613,7 +4691,7 @@
       <c r="W155" s="5"/>
       <c r="X155" s="5"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:24" ht="15.75" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4639,7 +4717,7 @@
       <c r="W156" s="5"/>
       <c r="X156" s="5"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:24" ht="15.75" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4665,7 +4743,7 @@
       <c r="W157" s="5"/>
       <c r="X157" s="5"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:24" ht="15.75" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4691,7 +4769,7 @@
       <c r="W158" s="5"/>
       <c r="X158" s="5"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:24" ht="15.75" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4717,7 +4795,7 @@
       <c r="W159" s="5"/>
       <c r="X159" s="5"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:24" ht="15.75" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4743,7 +4821,7 @@
       <c r="W160" s="5"/>
       <c r="X160" s="5"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:24" ht="15.75" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4769,7 +4847,7 @@
       <c r="W161" s="5"/>
       <c r="X161" s="5"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:24" ht="15.75" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4795,7 +4873,7 @@
       <c r="W162" s="5"/>
       <c r="X162" s="5"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:24" ht="15.75" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4821,7 +4899,7 @@
       <c r="W163" s="5"/>
       <c r="X163" s="5"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:24" ht="15.75" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4847,7 +4925,7 @@
       <c r="W164" s="5"/>
       <c r="X164" s="5"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:24" ht="15.75" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4873,7 +4951,7 @@
       <c r="W165" s="5"/>
       <c r="X165" s="5"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:24" ht="15.75" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4899,7 +4977,7 @@
       <c r="W166" s="5"/>
       <c r="X166" s="5"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:24" ht="15.75" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4925,7 +5003,7 @@
       <c r="W167" s="5"/>
       <c r="X167" s="5"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:24" ht="15.75" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4951,7 +5029,7 @@
       <c r="W168" s="5"/>
       <c r="X168" s="5"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:24" ht="15.75" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4977,7 +5055,7 @@
       <c r="W169" s="5"/>
       <c r="X169" s="5"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:24" ht="15.75" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5003,7 +5081,7 @@
       <c r="W170" s="5"/>
       <c r="X170" s="5"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:24" ht="15.75" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5029,7 +5107,7 @@
       <c r="W171" s="5"/>
       <c r="X171" s="5"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:24" ht="15.75" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5055,7 +5133,7 @@
       <c r="W172" s="5"/>
       <c r="X172" s="5"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:24" ht="15.75" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5081,7 +5159,7 @@
       <c r="W173" s="5"/>
       <c r="X173" s="5"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:24" ht="15.75" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5107,7 +5185,7 @@
       <c r="W174" s="5"/>
       <c r="X174" s="5"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:24" ht="15.75" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5133,7 +5211,7 @@
       <c r="W175" s="5"/>
       <c r="X175" s="5"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:24" ht="15.75" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5159,7 +5237,7 @@
       <c r="W176" s="5"/>
       <c r="X176" s="5"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:24" ht="15.75" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5185,7 +5263,7 @@
       <c r="W177" s="5"/>
       <c r="X177" s="5"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:24" ht="15.75" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5211,7 +5289,7 @@
       <c r="W178" s="5"/>
       <c r="X178" s="5"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:24" ht="15.75" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5237,7 +5315,7 @@
       <c r="W179" s="5"/>
       <c r="X179" s="5"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:24" ht="15.75" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5263,7 +5341,7 @@
       <c r="W180" s="5"/>
       <c r="X180" s="5"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:24" ht="15.75" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5289,7 +5367,7 @@
       <c r="W181" s="5"/>
       <c r="X181" s="5"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:24" ht="15.75" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5315,7 +5393,7 @@
       <c r="W182" s="5"/>
       <c r="X182" s="5"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:24" ht="15.75" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5341,7 +5419,7 @@
       <c r="W183" s="5"/>
       <c r="X183" s="5"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:24" ht="15.75" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5367,7 +5445,7 @@
       <c r="W184" s="5"/>
       <c r="X184" s="5"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:24" ht="15.75" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5393,7 +5471,7 @@
       <c r="W185" s="5"/>
       <c r="X185" s="5"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:24" ht="15.75" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5419,7 +5497,7 @@
       <c r="W186" s="5"/>
       <c r="X186" s="5"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:24" ht="15.75" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5445,7 +5523,7 @@
       <c r="W187" s="5"/>
       <c r="X187" s="5"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:24" ht="15.75" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5471,7 +5549,7 @@
       <c r="W188" s="5"/>
       <c r="X188" s="5"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:24" ht="15.75" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5497,7 +5575,7 @@
       <c r="W189" s="5"/>
       <c r="X189" s="5"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:24" ht="15.75" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5523,7 +5601,7 @@
       <c r="W190" s="5"/>
       <c r="X190" s="5"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:24" ht="15.75" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5549,7 +5627,7 @@
       <c r="W191" s="5"/>
       <c r="X191" s="5"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:24" ht="15.75" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5575,7 +5653,7 @@
       <c r="W192" s="5"/>
       <c r="X192" s="5"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:24" ht="15.75" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5601,7 +5679,7 @@
       <c r="W193" s="5"/>
       <c r="X193" s="5"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:24" ht="15.75" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5627,7 +5705,7 @@
       <c r="W194" s="5"/>
       <c r="X194" s="5"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:24" ht="15.75" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5653,7 +5731,7 @@
       <c r="W195" s="5"/>
       <c r="X195" s="5"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:24" ht="15.75" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5679,7 +5757,7 @@
       <c r="W196" s="5"/>
       <c r="X196" s="5"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:24" ht="15.75" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5705,7 +5783,7 @@
       <c r="W197" s="5"/>
       <c r="X197" s="5"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:24" ht="15.75" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5731,7 +5809,7 @@
       <c r="W198" s="5"/>
       <c r="X198" s="5"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:24" ht="15.75" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5757,7 +5835,7 @@
       <c r="W199" s="5"/>
       <c r="X199" s="5"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:24" ht="15.75" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5783,7 +5861,7 @@
       <c r="W200" s="5"/>
       <c r="X200" s="5"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:24" ht="15.75" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5809,7 +5887,7 @@
       <c r="W201" s="5"/>
       <c r="X201" s="5"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:24" ht="15.75" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5835,7 +5913,7 @@
       <c r="W202" s="5"/>
       <c r="X202" s="5"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:24" ht="15.75" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5861,7 +5939,7 @@
       <c r="W203" s="5"/>
       <c r="X203" s="5"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:24" ht="15.75" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5887,7 +5965,7 @@
       <c r="W204" s="5"/>
       <c r="X204" s="5"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:24" ht="15.75" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5913,7 +5991,7 @@
       <c r="W205" s="5"/>
       <c r="X205" s="5"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:24" ht="15.75" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5939,7 +6017,7 @@
       <c r="W206" s="5"/>
       <c r="X206" s="5"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:24" ht="15.75" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5965,7 +6043,7 @@
       <c r="W207" s="5"/>
       <c r="X207" s="5"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:24" ht="15.75" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5991,7 +6069,7 @@
       <c r="W208" s="5"/>
       <c r="X208" s="5"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:24" ht="15.75" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -6017,7 +6095,7 @@
       <c r="W209" s="5"/>
       <c r="X209" s="5"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:24" ht="15.75" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -6043,7 +6121,7 @@
       <c r="W210" s="5"/>
       <c r="X210" s="5"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:24" ht="15.75" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -6069,7 +6147,7 @@
       <c r="W211" s="5"/>
       <c r="X211" s="5"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:24" ht="15.75" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -6095,7 +6173,7 @@
       <c r="W212" s="5"/>
       <c r="X212" s="5"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:24" ht="15.75" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -6121,7 +6199,7 @@
       <c r="W213" s="5"/>
       <c r="X213" s="5"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:24" ht="15.75" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -6147,7 +6225,7 @@
       <c r="W214" s="5"/>
       <c r="X214" s="5"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:24" ht="15.75" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -6173,7 +6251,7 @@
       <c r="W215" s="5"/>
       <c r="X215" s="5"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:24" ht="15.75" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -6199,7 +6277,7 @@
       <c r="W216" s="5"/>
       <c r="X216" s="5"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:24" ht="15.75" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -6225,7 +6303,7 @@
       <c r="W217" s="5"/>
       <c r="X217" s="5"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:24" ht="15.75" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -6251,7 +6329,7 @@
       <c r="W218" s="5"/>
       <c r="X218" s="5"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:24" ht="15.75" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -6277,7 +6355,7 @@
       <c r="W219" s="5"/>
       <c r="X219" s="5"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:24" ht="15.75" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -6303,10 +6381,10 @@
       <c r="W220" s="5"/>
       <c r="X220" s="5"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:24" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -7084,9 +7162,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -174,35 +174,35 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Pet_Fire_001</t>
+    <t>Sprites/UI/Icon/PetIcon_Fire_001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/UI/Icon/Pet_Fire_001</t>
+    <t>Sprites/UI/Icon/PetIcon_Water_001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Pet_Water_001</t>
+    <t>Sprites/UI/Icon/PetIcon_Earth_001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/UI/Icon/Pet_Water_001</t>
+    <t>Sprites/UI/Icon/PetIcon_Air_001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Pet_Earth_001</t>
+    <t>pet_fire_001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/UI/Icon/Pet_Earth_001</t>
+    <t>pet_water_002</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Pet_Air_001</t>
+    <t>pet_earth_003</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/UI/Icon/Pet_Air_001</t>
+    <t>pet_air_004</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -684,7 +684,7 @@
     </row>
     <row r="4" spans="1:24" ht="31.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>17</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -724,7 +724,7 @@
     </row>
     <row r="5" spans="1:24" ht="31.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>22</v>
@@ -745,7 +745,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -766,7 +766,7 @@
     </row>
     <row r="6" spans="1:24" ht="31.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>27</v>
@@ -785,7 +785,7 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -806,7 +806,7 @@
     </row>
     <row r="7" spans="1:24" ht="31.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>31</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>

--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26205" windowHeight="12135"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+  <si>
+    <t>아이디</t>
+  </si>
   <si>
     <t>이름</t>
   </si>
@@ -35,24 +30,20 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Carlito"/>
         <b/>
-        <sz val="409.55"/>
         <color rgb="FF000000"/>
-        <rFont val="Carlito"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <sz val="1100.0"/>
       </rPr>
       <t xml:space="preserve">엑티브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <rFont val="Carlito"/>
         <b/>
-        <sz val="409.55"/>
         <color rgb="FF000000"/>
-        <rFont val="Carlito"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <sz val="1000.0"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -60,24 +51,20 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Carlito"/>
         <b/>
-        <sz val="409.55"/>
         <color rgb="FF000000"/>
-        <rFont val="Carlito"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <sz val="1100.0"/>
       </rPr>
       <t xml:space="preserve">패시브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <rFont val="Carlito"/>
         <b/>
-        <sz val="409.55"/>
         <color rgb="FF000000"/>
-        <rFont val="Carlito"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <sz val="1000.0"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -116,6 +103,9 @@
     <t>IconPath</t>
   </si>
   <si>
+    <t>pet_fire_001</t>
+  </si>
+  <si>
     <t>플레임폰</t>
   </si>
   <si>
@@ -129,6 +119,9 @@
   </si>
   <si>
     <t>pet_skill_fire_001</t>
+  </si>
+  <si>
+    <t>pet_water_002</t>
   </si>
   <si>
     <t>워터폰</t>
@@ -146,6 +139,9 @@
     <t>pet_passive_water_regeneration</t>
   </si>
   <si>
+    <t>pet_earth_003</t>
+  </si>
+  <si>
     <t>어스폰</t>
   </si>
   <si>
@@ -156,6 +152,9 @@
   </si>
   <si>
     <t>pet_skill_earth_001,pet_skill_taunt</t>
+  </si>
+  <si>
+    <t>pet_air_004</t>
   </si>
   <si>
     <t>윈드폰</t>
@@ -169,99 +168,41 @@
   <si>
     <t>pet_skill_air_001,pet_skill_windblessing</t>
   </si>
-  <si>
-    <t>아이디</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Icon/PetIcon_Fire_001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Icon/PetIcon_Water_001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Icon/PetIcon_Earth_001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Icon/PetIcon_Air_001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>pet_fire_001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>pet_water_002</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>pet_earth_003</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>pet_air_004</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="409.55"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Carlito"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -269,21 +210,9 @@
         <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA9999"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -297,47 +226,40 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="6">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -345,7 +267,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -535,51 +457,50 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="7.75" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="54.5" customWidth="1"/>
-    <col min="7" max="7" width="44.875" customWidth="1"/>
-    <col min="8" max="8" width="53.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="24" width="13" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="20.5"/>
+    <col customWidth="1" min="2" max="2" width="7.75"/>
+    <col customWidth="1" min="3" max="3" width="15.25"/>
+    <col customWidth="1" min="4" max="4" width="56.0"/>
+    <col customWidth="1" min="5" max="5" width="16.0"/>
+    <col customWidth="1" min="6" max="6" width="28.0"/>
+    <col customWidth="1" min="7" max="7" width="27.63"/>
+    <col customWidth="1" min="8" max="24" width="13.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="31.5" customHeight="1">
+    <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -598,30 +519,30 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:24" ht="24" customHeight="1">
+    <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -640,30 +561,30 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="27.75" customHeight="1">
+    <row r="3" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -682,29 +603,27 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:24" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -722,31 +641,29 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" spans="1:24" ht="31.5" customHeight="1">
+    <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -764,29 +681,27 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" spans="1:24" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -804,29 +719,27 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" spans="1:24" ht="31.5" customHeight="1">
+    <row r="7" ht="31.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -844,7 +757,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8" spans="1:24" ht="13.5">
+    <row r="8">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -870,7 +783,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9" spans="1:24" ht="13.5">
+    <row r="9">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -896,7 +809,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10" spans="1:24" ht="13.5">
+    <row r="10">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -922,7 +835,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11" spans="1:24" ht="13.5">
+    <row r="11">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -948,7 +861,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12" spans="1:24" ht="13.5">
+    <row r="12">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -974,7 +887,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13" spans="1:24" ht="13.5">
+    <row r="13">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1000,7 +913,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14" spans="1:24" ht="13.5">
+    <row r="14">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1025,7 +938,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15" spans="1:24" ht="13.5">
+    <row r="15">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1051,7 +964,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:24" ht="13.5">
+    <row r="16">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1077,7 +990,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17" spans="1:24" ht="13.5">
+    <row r="17">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1103,7 +1016,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="13.5">
+    <row r="18">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1129,7 +1042,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19" spans="1:24" ht="13.5">
+    <row r="19">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1155,7 +1068,7 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
-    <row r="20" spans="1:24" ht="13.5">
+    <row r="20">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1181,7 +1094,7 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1207,7 +1120,7 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" spans="1:24" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1233,7 +1146,7 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
     </row>
-    <row r="23" spans="1:24" ht="15.75" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1259,7 +1172,7 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" spans="1:24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1285,7 +1198,7 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
     </row>
-    <row r="25" spans="1:24" ht="15.75" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1311,7 +1224,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" spans="1:24" ht="15.75" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1337,7 +1250,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
     </row>
-    <row r="27" spans="1:24" ht="15.75" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1363,7 +1276,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
     </row>
-    <row r="28" spans="1:24" ht="15.75" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1389,7 +1302,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" spans="1:24" ht="15.75" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1415,7 +1328,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" spans="1:24" ht="15.75" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1441,7 +1354,7 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
     </row>
-    <row r="31" spans="1:24" ht="15.75" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1467,7 +1380,7 @@
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
     </row>
-    <row r="32" spans="1:24" ht="15.75" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1493,7 +1406,7 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
     </row>
-    <row r="33" spans="1:24" ht="15.75" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1519,7 +1432,7 @@
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
     </row>
-    <row r="34" spans="1:24" ht="15.75" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1545,7 +1458,7 @@
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
     </row>
-    <row r="35" spans="1:24" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1571,7 +1484,7 @@
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
     </row>
-    <row r="36" spans="1:24" ht="15.75" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1597,7 +1510,7 @@
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
     </row>
-    <row r="37" spans="1:24" ht="15.75" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1623,7 +1536,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
     </row>
-    <row r="38" spans="1:24" ht="15.75" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1649,7 +1562,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
     </row>
-    <row r="39" spans="1:24" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1675,7 +1588,7 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
-    <row r="40" spans="1:24" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1701,7 +1614,7 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
     </row>
-    <row r="41" spans="1:24" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1727,7 +1640,7 @@
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1753,7 +1666,7 @@
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1779,7 +1692,7 @@
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
     </row>
-    <row r="44" spans="1:24" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1805,7 +1718,7 @@
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
     </row>
-    <row r="45" spans="1:24" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1831,7 +1744,7 @@
       <c r="W45" s="5"/>
       <c r="X45" s="5"/>
     </row>
-    <row r="46" spans="1:24" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1857,7 +1770,7 @@
       <c r="W46" s="5"/>
       <c r="X46" s="5"/>
     </row>
-    <row r="47" spans="1:24" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1883,7 +1796,7 @@
       <c r="W47" s="5"/>
       <c r="X47" s="5"/>
     </row>
-    <row r="48" spans="1:24" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1909,7 +1822,7 @@
       <c r="W48" s="5"/>
       <c r="X48" s="5"/>
     </row>
-    <row r="49" spans="1:24" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1935,7 +1848,7 @@
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" spans="1:24" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1961,7 +1874,7 @@
       <c r="W50" s="5"/>
       <c r="X50" s="5"/>
     </row>
-    <row r="51" spans="1:24" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1987,7 +1900,7 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
     </row>
-    <row r="52" spans="1:24" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2013,7 +1926,7 @@
       <c r="W52" s="5"/>
       <c r="X52" s="5"/>
     </row>
-    <row r="53" spans="1:24" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2039,7 +1952,7 @@
       <c r="W53" s="5"/>
       <c r="X53" s="5"/>
     </row>
-    <row r="54" spans="1:24" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2065,7 +1978,7 @@
       <c r="W54" s="5"/>
       <c r="X54" s="5"/>
     </row>
-    <row r="55" spans="1:24" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2091,7 +2004,7 @@
       <c r="W55" s="5"/>
       <c r="X55" s="5"/>
     </row>
-    <row r="56" spans="1:24" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2117,7 +2030,7 @@
       <c r="W56" s="5"/>
       <c r="X56" s="5"/>
     </row>
-    <row r="57" spans="1:24" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2143,7 +2056,7 @@
       <c r="W57" s="5"/>
       <c r="X57" s="5"/>
     </row>
-    <row r="58" spans="1:24" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2169,7 +2082,7 @@
       <c r="W58" s="5"/>
       <c r="X58" s="5"/>
     </row>
-    <row r="59" spans="1:24" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2195,7 +2108,7 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
     </row>
-    <row r="60" spans="1:24" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2221,7 +2134,7 @@
       <c r="W60" s="5"/>
       <c r="X60" s="5"/>
     </row>
-    <row r="61" spans="1:24" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2247,7 +2160,7 @@
       <c r="W61" s="5"/>
       <c r="X61" s="5"/>
     </row>
-    <row r="62" spans="1:24" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2273,7 +2186,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" spans="1:24" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2299,7 +2212,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" spans="1:24" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2325,7 +2238,7 @@
       <c r="W64" s="5"/>
       <c r="X64" s="5"/>
     </row>
-    <row r="65" spans="1:24" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2351,7 +2264,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="1:24" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2377,7 +2290,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" spans="1:24" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2403,7 +2316,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
     </row>
-    <row r="68" spans="1:24" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2429,7 +2342,7 @@
       <c r="W68" s="5"/>
       <c r="X68" s="5"/>
     </row>
-    <row r="69" spans="1:24" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2455,7 +2368,7 @@
       <c r="W69" s="5"/>
       <c r="X69" s="5"/>
     </row>
-    <row r="70" spans="1:24" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2481,7 +2394,7 @@
       <c r="W70" s="5"/>
       <c r="X70" s="5"/>
     </row>
-    <row r="71" spans="1:24" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2507,7 +2420,7 @@
       <c r="W71" s="5"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" spans="1:24" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2533,7 +2446,7 @@
       <c r="W72" s="5"/>
       <c r="X72" s="5"/>
     </row>
-    <row r="73" spans="1:24" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2559,7 +2472,7 @@
       <c r="W73" s="5"/>
       <c r="X73" s="5"/>
     </row>
-    <row r="74" spans="1:24" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2585,7 +2498,7 @@
       <c r="W74" s="5"/>
       <c r="X74" s="5"/>
     </row>
-    <row r="75" spans="1:24" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2611,7 +2524,7 @@
       <c r="W75" s="5"/>
       <c r="X75" s="5"/>
     </row>
-    <row r="76" spans="1:24" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2637,7 +2550,7 @@
       <c r="W76" s="5"/>
       <c r="X76" s="5"/>
     </row>
-    <row r="77" spans="1:24" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2663,7 +2576,7 @@
       <c r="W77" s="5"/>
       <c r="X77" s="5"/>
     </row>
-    <row r="78" spans="1:24" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2689,7 +2602,7 @@
       <c r="W78" s="5"/>
       <c r="X78" s="5"/>
     </row>
-    <row r="79" spans="1:24" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2715,7 +2628,7 @@
       <c r="W79" s="5"/>
       <c r="X79" s="5"/>
     </row>
-    <row r="80" spans="1:24" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2741,7 +2654,7 @@
       <c r="W80" s="5"/>
       <c r="X80" s="5"/>
     </row>
-    <row r="81" spans="1:24" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2767,7 +2680,7 @@
       <c r="W81" s="5"/>
       <c r="X81" s="5"/>
     </row>
-    <row r="82" spans="1:24" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2793,7 +2706,7 @@
       <c r="W82" s="5"/>
       <c r="X82" s="5"/>
     </row>
-    <row r="83" spans="1:24" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2819,7 +2732,7 @@
       <c r="W83" s="5"/>
       <c r="X83" s="5"/>
     </row>
-    <row r="84" spans="1:24" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2845,7 +2758,7 @@
       <c r="W84" s="5"/>
       <c r="X84" s="5"/>
     </row>
-    <row r="85" spans="1:24" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2871,7 +2784,7 @@
       <c r="W85" s="5"/>
       <c r="X85" s="5"/>
     </row>
-    <row r="86" spans="1:24" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2897,7 +2810,7 @@
       <c r="W86" s="5"/>
       <c r="X86" s="5"/>
     </row>
-    <row r="87" spans="1:24" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2923,7 +2836,7 @@
       <c r="W87" s="5"/>
       <c r="X87" s="5"/>
     </row>
-    <row r="88" spans="1:24" ht="15.75" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2949,7 +2862,7 @@
       <c r="W88" s="5"/>
       <c r="X88" s="5"/>
     </row>
-    <row r="89" spans="1:24" ht="15.75" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2975,7 +2888,7 @@
       <c r="W89" s="5"/>
       <c r="X89" s="5"/>
     </row>
-    <row r="90" spans="1:24" ht="15.75" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3001,7 +2914,7 @@
       <c r="W90" s="5"/>
       <c r="X90" s="5"/>
     </row>
-    <row r="91" spans="1:24" ht="15.75" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3027,7 +2940,7 @@
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
     </row>
-    <row r="92" spans="1:24" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3053,7 +2966,7 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="93" spans="1:24" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3079,7 +2992,7 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
     </row>
-    <row r="94" spans="1:24" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3105,7 +3018,7 @@
       <c r="W94" s="5"/>
       <c r="X94" s="5"/>
     </row>
-    <row r="95" spans="1:24" ht="15.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3131,7 +3044,7 @@
       <c r="W95" s="5"/>
       <c r="X95" s="5"/>
     </row>
-    <row r="96" spans="1:24" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3157,7 +3070,7 @@
       <c r="W96" s="5"/>
       <c r="X96" s="5"/>
     </row>
-    <row r="97" spans="1:24" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3183,7 +3096,7 @@
       <c r="W97" s="5"/>
       <c r="X97" s="5"/>
     </row>
-    <row r="98" spans="1:24" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3209,7 +3122,7 @@
       <c r="W98" s="5"/>
       <c r="X98" s="5"/>
     </row>
-    <row r="99" spans="1:24" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3235,7 +3148,7 @@
       <c r="W99" s="5"/>
       <c r="X99" s="5"/>
     </row>
-    <row r="100" spans="1:24" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3261,7 +3174,7 @@
       <c r="W100" s="5"/>
       <c r="X100" s="5"/>
     </row>
-    <row r="101" spans="1:24" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3287,7 +3200,7 @@
       <c r="W101" s="5"/>
       <c r="X101" s="5"/>
     </row>
-    <row r="102" spans="1:24" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3313,7 +3226,7 @@
       <c r="W102" s="5"/>
       <c r="X102" s="5"/>
     </row>
-    <row r="103" spans="1:24" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3339,7 +3252,7 @@
       <c r="W103" s="5"/>
       <c r="X103" s="5"/>
     </row>
-    <row r="104" spans="1:24" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3365,7 +3278,7 @@
       <c r="W104" s="5"/>
       <c r="X104" s="5"/>
     </row>
-    <row r="105" spans="1:24" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3391,7 +3304,7 @@
       <c r="W105" s="5"/>
       <c r="X105" s="5"/>
     </row>
-    <row r="106" spans="1:24" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3417,7 +3330,7 @@
       <c r="W106" s="5"/>
       <c r="X106" s="5"/>
     </row>
-    <row r="107" spans="1:24" ht="15.75" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3443,7 +3356,7 @@
       <c r="W107" s="5"/>
       <c r="X107" s="5"/>
     </row>
-    <row r="108" spans="1:24" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3469,7 +3382,7 @@
       <c r="W108" s="5"/>
       <c r="X108" s="5"/>
     </row>
-    <row r="109" spans="1:24" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3495,7 +3408,7 @@
       <c r="W109" s="5"/>
       <c r="X109" s="5"/>
     </row>
-    <row r="110" spans="1:24" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3521,7 +3434,7 @@
       <c r="W110" s="5"/>
       <c r="X110" s="5"/>
     </row>
-    <row r="111" spans="1:24" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3547,7 +3460,7 @@
       <c r="W111" s="5"/>
       <c r="X111" s="5"/>
     </row>
-    <row r="112" spans="1:24" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3573,7 +3486,7 @@
       <c r="W112" s="5"/>
       <c r="X112" s="5"/>
     </row>
-    <row r="113" spans="1:24" ht="15.75" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3599,7 +3512,7 @@
       <c r="W113" s="5"/>
       <c r="X113" s="5"/>
     </row>
-    <row r="114" spans="1:24" ht="15.75" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3625,7 +3538,7 @@
       <c r="W114" s="5"/>
       <c r="X114" s="5"/>
     </row>
-    <row r="115" spans="1:24" ht="15.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3651,7 +3564,7 @@
       <c r="W115" s="5"/>
       <c r="X115" s="5"/>
     </row>
-    <row r="116" spans="1:24" ht="15.75" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3677,7 +3590,7 @@
       <c r="W116" s="5"/>
       <c r="X116" s="5"/>
     </row>
-    <row r="117" spans="1:24" ht="15.75" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3703,7 +3616,7 @@
       <c r="W117" s="5"/>
       <c r="X117" s="5"/>
     </row>
-    <row r="118" spans="1:24" ht="15.75" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3729,7 +3642,7 @@
       <c r="W118" s="5"/>
       <c r="X118" s="5"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3755,7 +3668,7 @@
       <c r="W119" s="5"/>
       <c r="X119" s="5"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3781,7 +3694,7 @@
       <c r="W120" s="5"/>
       <c r="X120" s="5"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3807,7 +3720,7 @@
       <c r="W121" s="5"/>
       <c r="X121" s="5"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3833,7 +3746,7 @@
       <c r="W122" s="5"/>
       <c r="X122" s="5"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3859,7 +3772,7 @@
       <c r="W123" s="5"/>
       <c r="X123" s="5"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3885,7 +3798,7 @@
       <c r="W124" s="5"/>
       <c r="X124" s="5"/>
     </row>
-    <row r="125" spans="1:24" ht="15.75" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3911,7 +3824,7 @@
       <c r="W125" s="5"/>
       <c r="X125" s="5"/>
     </row>
-    <row r="126" spans="1:24" ht="15.75" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3937,7 +3850,7 @@
       <c r="W126" s="5"/>
       <c r="X126" s="5"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3963,7 +3876,7 @@
       <c r="W127" s="5"/>
       <c r="X127" s="5"/>
     </row>
-    <row r="128" spans="1:24" ht="15.75" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3989,7 +3902,7 @@
       <c r="W128" s="5"/>
       <c r="X128" s="5"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4015,7 +3928,7 @@
       <c r="W129" s="5"/>
       <c r="X129" s="5"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4041,7 +3954,7 @@
       <c r="W130" s="5"/>
       <c r="X130" s="5"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4067,7 +3980,7 @@
       <c r="W131" s="5"/>
       <c r="X131" s="5"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4093,7 +4006,7 @@
       <c r="W132" s="5"/>
       <c r="X132" s="5"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4119,7 +4032,7 @@
       <c r="W133" s="5"/>
       <c r="X133" s="5"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4145,7 +4058,7 @@
       <c r="W134" s="5"/>
       <c r="X134" s="5"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4171,7 +4084,7 @@
       <c r="W135" s="5"/>
       <c r="X135" s="5"/>
     </row>
-    <row r="136" spans="1:24" ht="15.75" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4197,7 +4110,7 @@
       <c r="W136" s="5"/>
       <c r="X136" s="5"/>
     </row>
-    <row r="137" spans="1:24" ht="15.75" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4223,7 +4136,7 @@
       <c r="W137" s="5"/>
       <c r="X137" s="5"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4249,7 +4162,7 @@
       <c r="W138" s="5"/>
       <c r="X138" s="5"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" customHeight="1">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4275,7 +4188,7 @@
       <c r="W139" s="5"/>
       <c r="X139" s="5"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4301,7 +4214,7 @@
       <c r="W140" s="5"/>
       <c r="X140" s="5"/>
     </row>
-    <row r="141" spans="1:24" ht="15.75" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4327,7 +4240,7 @@
       <c r="W141" s="5"/>
       <c r="X141" s="5"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4353,7 +4266,7 @@
       <c r="W142" s="5"/>
       <c r="X142" s="5"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4379,7 +4292,7 @@
       <c r="W143" s="5"/>
       <c r="X143" s="5"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4405,7 +4318,7 @@
       <c r="W144" s="5"/>
       <c r="X144" s="5"/>
     </row>
-    <row r="145" spans="1:24" ht="15.75" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4431,7 +4344,7 @@
       <c r="W145" s="5"/>
       <c r="X145" s="5"/>
     </row>
-    <row r="146" spans="1:24" ht="15.75" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4457,7 +4370,7 @@
       <c r="W146" s="5"/>
       <c r="X146" s="5"/>
     </row>
-    <row r="147" spans="1:24" ht="15.75" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4483,7 +4396,7 @@
       <c r="W147" s="5"/>
       <c r="X147" s="5"/>
     </row>
-    <row r="148" spans="1:24" ht="15.75" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4509,7 +4422,7 @@
       <c r="W148" s="5"/>
       <c r="X148" s="5"/>
     </row>
-    <row r="149" spans="1:24" ht="15.75" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4535,7 +4448,7 @@
       <c r="W149" s="5"/>
       <c r="X149" s="5"/>
     </row>
-    <row r="150" spans="1:24" ht="15.75" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4561,7 +4474,7 @@
       <c r="W150" s="5"/>
       <c r="X150" s="5"/>
     </row>
-    <row r="151" spans="1:24" ht="15.75" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4587,7 +4500,7 @@
       <c r="W151" s="5"/>
       <c r="X151" s="5"/>
     </row>
-    <row r="152" spans="1:24" ht="15.75" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4613,7 +4526,7 @@
       <c r="W152" s="5"/>
       <c r="X152" s="5"/>
     </row>
-    <row r="153" spans="1:24" ht="15.75" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4639,7 +4552,7 @@
       <c r="W153" s="5"/>
       <c r="X153" s="5"/>
     </row>
-    <row r="154" spans="1:24" ht="15.75" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4665,7 +4578,7 @@
       <c r="W154" s="5"/>
       <c r="X154" s="5"/>
     </row>
-    <row r="155" spans="1:24" ht="15.75" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4691,7 +4604,7 @@
       <c r="W155" s="5"/>
       <c r="X155" s="5"/>
     </row>
-    <row r="156" spans="1:24" ht="15.75" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4717,7 +4630,7 @@
       <c r="W156" s="5"/>
       <c r="X156" s="5"/>
     </row>
-    <row r="157" spans="1:24" ht="15.75" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4743,7 +4656,7 @@
       <c r="W157" s="5"/>
       <c r="X157" s="5"/>
     </row>
-    <row r="158" spans="1:24" ht="15.75" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4769,7 +4682,7 @@
       <c r="W158" s="5"/>
       <c r="X158" s="5"/>
     </row>
-    <row r="159" spans="1:24" ht="15.75" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4795,7 +4708,7 @@
       <c r="W159" s="5"/>
       <c r="X159" s="5"/>
     </row>
-    <row r="160" spans="1:24" ht="15.75" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4821,7 +4734,7 @@
       <c r="W160" s="5"/>
       <c r="X160" s="5"/>
     </row>
-    <row r="161" spans="1:24" ht="15.75" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4847,7 +4760,7 @@
       <c r="W161" s="5"/>
       <c r="X161" s="5"/>
     </row>
-    <row r="162" spans="1:24" ht="15.75" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4873,7 +4786,7 @@
       <c r="W162" s="5"/>
       <c r="X162" s="5"/>
     </row>
-    <row r="163" spans="1:24" ht="15.75" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4899,7 +4812,7 @@
       <c r="W163" s="5"/>
       <c r="X163" s="5"/>
     </row>
-    <row r="164" spans="1:24" ht="15.75" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4925,7 +4838,7 @@
       <c r="W164" s="5"/>
       <c r="X164" s="5"/>
     </row>
-    <row r="165" spans="1:24" ht="15.75" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4951,7 +4864,7 @@
       <c r="W165" s="5"/>
       <c r="X165" s="5"/>
     </row>
-    <row r="166" spans="1:24" ht="15.75" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4977,7 +4890,7 @@
       <c r="W166" s="5"/>
       <c r="X166" s="5"/>
     </row>
-    <row r="167" spans="1:24" ht="15.75" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5003,7 +4916,7 @@
       <c r="W167" s="5"/>
       <c r="X167" s="5"/>
     </row>
-    <row r="168" spans="1:24" ht="15.75" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5029,7 +4942,7 @@
       <c r="W168" s="5"/>
       <c r="X168" s="5"/>
     </row>
-    <row r="169" spans="1:24" ht="15.75" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5055,7 +4968,7 @@
       <c r="W169" s="5"/>
       <c r="X169" s="5"/>
     </row>
-    <row r="170" spans="1:24" ht="15.75" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5081,7 +4994,7 @@
       <c r="W170" s="5"/>
       <c r="X170" s="5"/>
     </row>
-    <row r="171" spans="1:24" ht="15.75" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5107,7 +5020,7 @@
       <c r="W171" s="5"/>
       <c r="X171" s="5"/>
     </row>
-    <row r="172" spans="1:24" ht="15.75" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5133,7 +5046,7 @@
       <c r="W172" s="5"/>
       <c r="X172" s="5"/>
     </row>
-    <row r="173" spans="1:24" ht="15.75" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5159,7 +5072,7 @@
       <c r="W173" s="5"/>
       <c r="X173" s="5"/>
     </row>
-    <row r="174" spans="1:24" ht="15.75" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5185,7 +5098,7 @@
       <c r="W174" s="5"/>
       <c r="X174" s="5"/>
     </row>
-    <row r="175" spans="1:24" ht="15.75" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5211,7 +5124,7 @@
       <c r="W175" s="5"/>
       <c r="X175" s="5"/>
     </row>
-    <row r="176" spans="1:24" ht="15.75" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5237,7 +5150,7 @@
       <c r="W176" s="5"/>
       <c r="X176" s="5"/>
     </row>
-    <row r="177" spans="1:24" ht="15.75" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5263,7 +5176,7 @@
       <c r="W177" s="5"/>
       <c r="X177" s="5"/>
     </row>
-    <row r="178" spans="1:24" ht="15.75" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5289,7 +5202,7 @@
       <c r="W178" s="5"/>
       <c r="X178" s="5"/>
     </row>
-    <row r="179" spans="1:24" ht="15.75" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5315,7 +5228,7 @@
       <c r="W179" s="5"/>
       <c r="X179" s="5"/>
     </row>
-    <row r="180" spans="1:24" ht="15.75" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5341,7 +5254,7 @@
       <c r="W180" s="5"/>
       <c r="X180" s="5"/>
     </row>
-    <row r="181" spans="1:24" ht="15.75" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5367,7 +5280,7 @@
       <c r="W181" s="5"/>
       <c r="X181" s="5"/>
     </row>
-    <row r="182" spans="1:24" ht="15.75" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5393,7 +5306,7 @@
       <c r="W182" s="5"/>
       <c r="X182" s="5"/>
     </row>
-    <row r="183" spans="1:24" ht="15.75" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5419,7 +5332,7 @@
       <c r="W183" s="5"/>
       <c r="X183" s="5"/>
     </row>
-    <row r="184" spans="1:24" ht="15.75" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5445,7 +5358,7 @@
       <c r="W184" s="5"/>
       <c r="X184" s="5"/>
     </row>
-    <row r="185" spans="1:24" ht="15.75" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5471,7 +5384,7 @@
       <c r="W185" s="5"/>
       <c r="X185" s="5"/>
     </row>
-    <row r="186" spans="1:24" ht="15.75" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5497,7 +5410,7 @@
       <c r="W186" s="5"/>
       <c r="X186" s="5"/>
     </row>
-    <row r="187" spans="1:24" ht="15.75" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5523,7 +5436,7 @@
       <c r="W187" s="5"/>
       <c r="X187" s="5"/>
     </row>
-    <row r="188" spans="1:24" ht="15.75" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5549,7 +5462,7 @@
       <c r="W188" s="5"/>
       <c r="X188" s="5"/>
     </row>
-    <row r="189" spans="1:24" ht="15.75" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5575,7 +5488,7 @@
       <c r="W189" s="5"/>
       <c r="X189" s="5"/>
     </row>
-    <row r="190" spans="1:24" ht="15.75" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5601,7 +5514,7 @@
       <c r="W190" s="5"/>
       <c r="X190" s="5"/>
     </row>
-    <row r="191" spans="1:24" ht="15.75" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5627,7 +5540,7 @@
       <c r="W191" s="5"/>
       <c r="X191" s="5"/>
     </row>
-    <row r="192" spans="1:24" ht="15.75" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5653,7 +5566,7 @@
       <c r="W192" s="5"/>
       <c r="X192" s="5"/>
     </row>
-    <row r="193" spans="1:24" ht="15.75" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5679,7 +5592,7 @@
       <c r="W193" s="5"/>
       <c r="X193" s="5"/>
     </row>
-    <row r="194" spans="1:24" ht="15.75" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5705,7 +5618,7 @@
       <c r="W194" s="5"/>
       <c r="X194" s="5"/>
     </row>
-    <row r="195" spans="1:24" ht="15.75" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5731,7 +5644,7 @@
       <c r="W195" s="5"/>
       <c r="X195" s="5"/>
     </row>
-    <row r="196" spans="1:24" ht="15.75" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5757,7 +5670,7 @@
       <c r="W196" s="5"/>
       <c r="X196" s="5"/>
     </row>
-    <row r="197" spans="1:24" ht="15.75" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5783,7 +5696,7 @@
       <c r="W197" s="5"/>
       <c r="X197" s="5"/>
     </row>
-    <row r="198" spans="1:24" ht="15.75" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5809,7 +5722,7 @@
       <c r="W198" s="5"/>
       <c r="X198" s="5"/>
     </row>
-    <row r="199" spans="1:24" ht="15.75" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5835,7 +5748,7 @@
       <c r="W199" s="5"/>
       <c r="X199" s="5"/>
     </row>
-    <row r="200" spans="1:24" ht="15.75" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5861,7 +5774,7 @@
       <c r="W200" s="5"/>
       <c r="X200" s="5"/>
     </row>
-    <row r="201" spans="1:24" ht="15.75" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5887,7 +5800,7 @@
       <c r="W201" s="5"/>
       <c r="X201" s="5"/>
     </row>
-    <row r="202" spans="1:24" ht="15.75" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5913,7 +5826,7 @@
       <c r="W202" s="5"/>
       <c r="X202" s="5"/>
     </row>
-    <row r="203" spans="1:24" ht="15.75" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5939,7 +5852,7 @@
       <c r="W203" s="5"/>
       <c r="X203" s="5"/>
     </row>
-    <row r="204" spans="1:24" ht="15.75" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5965,7 +5878,7 @@
       <c r="W204" s="5"/>
       <c r="X204" s="5"/>
     </row>
-    <row r="205" spans="1:24" ht="15.75" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5991,7 +5904,7 @@
       <c r="W205" s="5"/>
       <c r="X205" s="5"/>
     </row>
-    <row r="206" spans="1:24" ht="15.75" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -6017,7 +5930,7 @@
       <c r="W206" s="5"/>
       <c r="X206" s="5"/>
     </row>
-    <row r="207" spans="1:24" ht="15.75" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -6043,7 +5956,7 @@
       <c r="W207" s="5"/>
       <c r="X207" s="5"/>
     </row>
-    <row r="208" spans="1:24" ht="15.75" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -6069,7 +5982,7 @@
       <c r="W208" s="5"/>
       <c r="X208" s="5"/>
     </row>
-    <row r="209" spans="1:24" ht="15.75" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -6095,7 +6008,7 @@
       <c r="W209" s="5"/>
       <c r="X209" s="5"/>
     </row>
-    <row r="210" spans="1:24" ht="15.75" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -6121,7 +6034,7 @@
       <c r="W210" s="5"/>
       <c r="X210" s="5"/>
     </row>
-    <row r="211" spans="1:24" ht="15.75" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -6147,7 +6060,7 @@
       <c r="W211" s="5"/>
       <c r="X211" s="5"/>
     </row>
-    <row r="212" spans="1:24" ht="15.75" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -6173,7 +6086,7 @@
       <c r="W212" s="5"/>
       <c r="X212" s="5"/>
     </row>
-    <row r="213" spans="1:24" ht="15.75" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -6199,7 +6112,7 @@
       <c r="W213" s="5"/>
       <c r="X213" s="5"/>
     </row>
-    <row r="214" spans="1:24" ht="15.75" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -6225,7 +6138,7 @@
       <c r="W214" s="5"/>
       <c r="X214" s="5"/>
     </row>
-    <row r="215" spans="1:24" ht="15.75" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -6251,7 +6164,7 @@
       <c r="W215" s="5"/>
       <c r="X215" s="5"/>
     </row>
-    <row r="216" spans="1:24" ht="15.75" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -6277,7 +6190,7 @@
       <c r="W216" s="5"/>
       <c r="X216" s="5"/>
     </row>
-    <row r="217" spans="1:24" ht="15.75" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -6303,7 +6216,7 @@
       <c r="W217" s="5"/>
       <c r="X217" s="5"/>
     </row>
-    <row r="218" spans="1:24" ht="15.75" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -6329,7 +6242,7 @@
       <c r="W218" s="5"/>
       <c r="X218" s="5"/>
     </row>
-    <row r="219" spans="1:24" ht="15.75" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -6355,7 +6268,7 @@
       <c r="W219" s="5"/>
       <c r="X219" s="5"/>
     </row>
-    <row r="220" spans="1:24" ht="15.75" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -6381,10 +6294,10 @@
       <c r="W220" s="5"/>
       <c r="X220" s="5"/>
     </row>
-    <row r="221" spans="1:24" ht="15.75" customHeight="1"/>
-    <row r="222" spans="1:24" ht="15.75" customHeight="1"/>
-    <row r="223" spans="1:24" ht="15.75" customHeight="1"/>
-    <row r="224" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -7162,8 +7075,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>아이디</t>
   </si>
@@ -30,20 +38,24 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1100.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">엑티브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1000.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -51,20 +63,24 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1100.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">패시브 스킬 id들
 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="409.55"/>
+        <color rgb="FF000000"/>
         <rFont val="Carlito"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="1000.0"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>ex) skill1,skill2 -&gt; 띄워쓰기 x</t>
     </r>
@@ -168,33 +184,75 @@
   <si>
     <t>pet_skill_air_001,pet_skill_windblessing</t>
   </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Fire_001</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Water_001</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Earth_001</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Air_001</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="409.55"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -202,7 +260,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -211,8 +269,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -226,40 +290,78 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -267,7 +369,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -457,27 +559,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.5"/>
-    <col customWidth="1" min="2" max="2" width="7.75"/>
-    <col customWidth="1" min="3" max="3" width="15.25"/>
-    <col customWidth="1" min="4" max="4" width="56.0"/>
-    <col customWidth="1" min="5" max="5" width="16.0"/>
-    <col customWidth="1" min="6" max="6" width="28.0"/>
-    <col customWidth="1" min="7" max="7" width="27.63"/>
-    <col customWidth="1" min="8" max="24" width="13.0"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="7.75" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="56" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="27.625" customWidth="1"/>
+    <col min="8" max="8" width="34.25" customWidth="1"/>
+    <col min="9" max="24" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:24" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +622,7 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" ht="24.0" customHeight="1">
+    <row r="2" spans="1:24" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -561,7 +664,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" ht="27.75" customHeight="1">
+    <row r="3" spans="1:24" ht="27.75" customHeight="1" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -603,7 +706,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
+    <row r="4" spans="1:24" ht="31.5" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -623,7 +726,9 @@
         <v>23</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -641,7 +746,7 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
+    <row r="5" spans="1:24" ht="31.5" customHeight="1" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
@@ -663,7 +768,9 @@
       <c r="G5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -681,7 +788,7 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1">
+    <row r="6" spans="1:24" ht="31.5" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -701,7 +808,9 @@
         <v>34</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -719,7 +828,7 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1">
+    <row r="7" spans="1:24" ht="31.5" customHeight="1" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>35</v>
       </c>
@@ -739,7 +848,9 @@
         <v>39</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -757,7 +868,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:24" ht="13.5">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -783,7 +894,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:24" ht="13.5">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -809,7 +920,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:24" ht="13.5">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -835,7 +946,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:24" ht="13.5">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -861,7 +972,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:24" ht="13.5">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -887,7 +998,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:24" ht="13.5">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -913,7 +1024,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:24" ht="13.5">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -938,7 +1049,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:24" ht="13.5">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -964,7 +1075,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:24" ht="13.5">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -990,7 +1101,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:24" ht="13.5">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1016,7 +1127,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:24" ht="13.5">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1042,7 +1153,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:24" ht="13.5">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1068,7 +1179,7 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:24" ht="13.5">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1094,7 +1205,7 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:24" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1120,7 +1231,7 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:24" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1146,7 +1257,7 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:24" ht="15.75" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1172,7 +1283,7 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:24" ht="15.75" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1198,7 +1309,7 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:24" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1224,7 +1335,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:24" ht="15.75" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1250,7 +1361,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:24" ht="15.75" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1276,7 +1387,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:24" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1302,7 +1413,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:24" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1328,7 +1439,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:24" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1354,7 +1465,7 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:24" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1380,7 +1491,7 @@
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:24" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1406,7 +1517,7 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:24" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1432,7 +1543,7 @@
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:24" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1458,7 +1569,7 @@
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:24" ht="15.75" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1484,7 +1595,7 @@
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:24" ht="15.75" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1510,7 +1621,7 @@
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:24" ht="15.75" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1536,7 +1647,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:24" ht="15.75" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1562,7 +1673,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:24" ht="15.75" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1588,7 +1699,7 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:24" ht="15.75" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1614,7 +1725,7 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:24" ht="15.75" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1640,7 +1751,7 @@
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:24" ht="15.75" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1666,7 +1777,7 @@
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:24" ht="15.75" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1692,7 +1803,7 @@
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:24" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1718,7 +1829,7 @@
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:24" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1744,7 +1855,7 @@
       <c r="W45" s="5"/>
       <c r="X45" s="5"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:24" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1770,7 +1881,7 @@
       <c r="W46" s="5"/>
       <c r="X46" s="5"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:24" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1796,7 +1907,7 @@
       <c r="W47" s="5"/>
       <c r="X47" s="5"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:24" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1822,7 +1933,7 @@
       <c r="W48" s="5"/>
       <c r="X48" s="5"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:24" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1848,7 +1959,7 @@
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:24" ht="15.75" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1874,7 +1985,7 @@
       <c r="W50" s="5"/>
       <c r="X50" s="5"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:24" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1900,7 +2011,7 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:24" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -1926,7 +2037,7 @@
       <c r="W52" s="5"/>
       <c r="X52" s="5"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:24" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1952,7 +2063,7 @@
       <c r="W53" s="5"/>
       <c r="X53" s="5"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:24" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1978,7 +2089,7 @@
       <c r="W54" s="5"/>
       <c r="X54" s="5"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:24" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2004,7 +2115,7 @@
       <c r="W55" s="5"/>
       <c r="X55" s="5"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:24" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2030,7 +2141,7 @@
       <c r="W56" s="5"/>
       <c r="X56" s="5"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:24" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2056,7 +2167,7 @@
       <c r="W57" s="5"/>
       <c r="X57" s="5"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:24" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2082,7 +2193,7 @@
       <c r="W58" s="5"/>
       <c r="X58" s="5"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:24" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2108,7 +2219,7 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:24" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2134,7 +2245,7 @@
       <c r="W60" s="5"/>
       <c r="X60" s="5"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:24" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2160,7 +2271,7 @@
       <c r="W61" s="5"/>
       <c r="X61" s="5"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:24" ht="15.75" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2186,7 +2297,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:24" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2212,7 +2323,7 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:24" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2238,7 +2349,7 @@
       <c r="W64" s="5"/>
       <c r="X64" s="5"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:24" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2264,7 +2375,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:24" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2290,7 +2401,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:24" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2316,7 +2427,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:24" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2342,7 +2453,7 @@
       <c r="W68" s="5"/>
       <c r="X68" s="5"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:24" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2368,7 +2479,7 @@
       <c r="W69" s="5"/>
       <c r="X69" s="5"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:24" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2394,7 +2505,7 @@
       <c r="W70" s="5"/>
       <c r="X70" s="5"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:24" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2420,7 +2531,7 @@
       <c r="W71" s="5"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:24" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2446,7 +2557,7 @@
       <c r="W72" s="5"/>
       <c r="X72" s="5"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:24" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2472,7 +2583,7 @@
       <c r="W73" s="5"/>
       <c r="X73" s="5"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:24" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2498,7 +2609,7 @@
       <c r="W74" s="5"/>
       <c r="X74" s="5"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:24" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2524,7 +2635,7 @@
       <c r="W75" s="5"/>
       <c r="X75" s="5"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:24" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2550,7 +2661,7 @@
       <c r="W76" s="5"/>
       <c r="X76" s="5"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:24" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2576,7 +2687,7 @@
       <c r="W77" s="5"/>
       <c r="X77" s="5"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:24" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2602,7 +2713,7 @@
       <c r="W78" s="5"/>
       <c r="X78" s="5"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:24" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2628,7 +2739,7 @@
       <c r="W79" s="5"/>
       <c r="X79" s="5"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:24" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2654,7 +2765,7 @@
       <c r="W80" s="5"/>
       <c r="X80" s="5"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:24" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2680,7 +2791,7 @@
       <c r="W81" s="5"/>
       <c r="X81" s="5"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:24" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2706,7 +2817,7 @@
       <c r="W82" s="5"/>
       <c r="X82" s="5"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:24" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2732,7 +2843,7 @@
       <c r="W83" s="5"/>
       <c r="X83" s="5"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:24" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2758,7 +2869,7 @@
       <c r="W84" s="5"/>
       <c r="X84" s="5"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:24" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2784,7 +2895,7 @@
       <c r="W85" s="5"/>
       <c r="X85" s="5"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:24" ht="15.75" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2810,7 +2921,7 @@
       <c r="W86" s="5"/>
       <c r="X86" s="5"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:24" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2836,7 +2947,7 @@
       <c r="W87" s="5"/>
       <c r="X87" s="5"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:24" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2862,7 +2973,7 @@
       <c r="W88" s="5"/>
       <c r="X88" s="5"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:24" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2888,7 +2999,7 @@
       <c r="W89" s="5"/>
       <c r="X89" s="5"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:24" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2914,7 +3025,7 @@
       <c r="W90" s="5"/>
       <c r="X90" s="5"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:24" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2940,7 +3051,7 @@
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:24" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2966,7 +3077,7 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:24" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2992,7 +3103,7 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:24" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3018,7 +3129,7 @@
       <c r="W94" s="5"/>
       <c r="X94" s="5"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:24" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3044,7 +3155,7 @@
       <c r="W95" s="5"/>
       <c r="X95" s="5"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:24" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3070,7 +3181,7 @@
       <c r="W96" s="5"/>
       <c r="X96" s="5"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:24" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3096,7 +3207,7 @@
       <c r="W97" s="5"/>
       <c r="X97" s="5"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:24" ht="15.75" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3122,7 +3233,7 @@
       <c r="W98" s="5"/>
       <c r="X98" s="5"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:24" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3148,7 +3259,7 @@
       <c r="W99" s="5"/>
       <c r="X99" s="5"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:24" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3174,7 +3285,7 @@
       <c r="W100" s="5"/>
       <c r="X100" s="5"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:24" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3200,7 +3311,7 @@
       <c r="W101" s="5"/>
       <c r="X101" s="5"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:24" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3226,7 +3337,7 @@
       <c r="W102" s="5"/>
       <c r="X102" s="5"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:24" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3252,7 +3363,7 @@
       <c r="W103" s="5"/>
       <c r="X103" s="5"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:24" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3278,7 +3389,7 @@
       <c r="W104" s="5"/>
       <c r="X104" s="5"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:24" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3304,7 +3415,7 @@
       <c r="W105" s="5"/>
       <c r="X105" s="5"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:24" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3330,7 +3441,7 @@
       <c r="W106" s="5"/>
       <c r="X106" s="5"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:24" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3356,7 +3467,7 @@
       <c r="W107" s="5"/>
       <c r="X107" s="5"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:24" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3382,7 +3493,7 @@
       <c r="W108" s="5"/>
       <c r="X108" s="5"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:24" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3408,7 +3519,7 @@
       <c r="W109" s="5"/>
       <c r="X109" s="5"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:24" ht="15.75" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3434,7 +3545,7 @@
       <c r="W110" s="5"/>
       <c r="X110" s="5"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:24" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3460,7 +3571,7 @@
       <c r="W111" s="5"/>
       <c r="X111" s="5"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:24" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3486,7 +3597,7 @@
       <c r="W112" s="5"/>
       <c r="X112" s="5"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:24" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3512,7 +3623,7 @@
       <c r="W113" s="5"/>
       <c r="X113" s="5"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:24" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3538,7 +3649,7 @@
       <c r="W114" s="5"/>
       <c r="X114" s="5"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:24" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3564,7 +3675,7 @@
       <c r="W115" s="5"/>
       <c r="X115" s="5"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:24" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3590,7 +3701,7 @@
       <c r="W116" s="5"/>
       <c r="X116" s="5"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:24" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3616,7 +3727,7 @@
       <c r="W117" s="5"/>
       <c r="X117" s="5"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:24" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3642,7 +3753,7 @@
       <c r="W118" s="5"/>
       <c r="X118" s="5"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:24" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3668,7 +3779,7 @@
       <c r="W119" s="5"/>
       <c r="X119" s="5"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:24" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3694,7 +3805,7 @@
       <c r="W120" s="5"/>
       <c r="X120" s="5"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3720,7 +3831,7 @@
       <c r="W121" s="5"/>
       <c r="X121" s="5"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:24" ht="15.75" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3746,7 +3857,7 @@
       <c r="W122" s="5"/>
       <c r="X122" s="5"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3772,7 +3883,7 @@
       <c r="W123" s="5"/>
       <c r="X123" s="5"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:24" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3798,7 +3909,7 @@
       <c r="W124" s="5"/>
       <c r="X124" s="5"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:24" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3824,7 +3935,7 @@
       <c r="W125" s="5"/>
       <c r="X125" s="5"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:24" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3850,7 +3961,7 @@
       <c r="W126" s="5"/>
       <c r="X126" s="5"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:24" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3876,7 +3987,7 @@
       <c r="W127" s="5"/>
       <c r="X127" s="5"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:24" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3902,7 +4013,7 @@
       <c r="W128" s="5"/>
       <c r="X128" s="5"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:24" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3928,7 +4039,7 @@
       <c r="W129" s="5"/>
       <c r="X129" s="5"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:24" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3954,7 +4065,7 @@
       <c r="W130" s="5"/>
       <c r="X130" s="5"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:24" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3980,7 +4091,7 @@
       <c r="W131" s="5"/>
       <c r="X131" s="5"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:24" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4006,7 +4117,7 @@
       <c r="W132" s="5"/>
       <c r="X132" s="5"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4032,7 +4143,7 @@
       <c r="W133" s="5"/>
       <c r="X133" s="5"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:24" ht="15.75" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4058,7 +4169,7 @@
       <c r="W134" s="5"/>
       <c r="X134" s="5"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:24" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4084,7 +4195,7 @@
       <c r="W135" s="5"/>
       <c r="X135" s="5"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:24" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4110,7 +4221,7 @@
       <c r="W136" s="5"/>
       <c r="X136" s="5"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:24" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4136,7 +4247,7 @@
       <c r="W137" s="5"/>
       <c r="X137" s="5"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:24" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4162,7 +4273,7 @@
       <c r="W138" s="5"/>
       <c r="X138" s="5"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:24" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4188,7 +4299,7 @@
       <c r="W139" s="5"/>
       <c r="X139" s="5"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:24" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4214,7 +4325,7 @@
       <c r="W140" s="5"/>
       <c r="X140" s="5"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:24" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4240,7 +4351,7 @@
       <c r="W141" s="5"/>
       <c r="X141" s="5"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:24" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4266,7 +4377,7 @@
       <c r="W142" s="5"/>
       <c r="X142" s="5"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:24" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4292,7 +4403,7 @@
       <c r="W143" s="5"/>
       <c r="X143" s="5"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:24" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4318,7 +4429,7 @@
       <c r="W144" s="5"/>
       <c r="X144" s="5"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:24" ht="15.75" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4344,7 +4455,7 @@
       <c r="W145" s="5"/>
       <c r="X145" s="5"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:24" ht="15.75" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4370,7 +4481,7 @@
       <c r="W146" s="5"/>
       <c r="X146" s="5"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:24" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4396,7 +4507,7 @@
       <c r="W147" s="5"/>
       <c r="X147" s="5"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:24" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4422,7 +4533,7 @@
       <c r="W148" s="5"/>
       <c r="X148" s="5"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:24" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4448,7 +4559,7 @@
       <c r="W149" s="5"/>
       <c r="X149" s="5"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:24" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4474,7 +4585,7 @@
       <c r="W150" s="5"/>
       <c r="X150" s="5"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:24" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4500,7 +4611,7 @@
       <c r="W151" s="5"/>
       <c r="X151" s="5"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:24" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4526,7 +4637,7 @@
       <c r="W152" s="5"/>
       <c r="X152" s="5"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:24" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4552,7 +4663,7 @@
       <c r="W153" s="5"/>
       <c r="X153" s="5"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:24" ht="15.75" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4578,7 +4689,7 @@
       <c r="W154" s="5"/>
       <c r="X154" s="5"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:24" ht="15.75" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4604,7 +4715,7 @@
       <c r="W155" s="5"/>
       <c r="X155" s="5"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:24" ht="15.75" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4630,7 +4741,7 @@
       <c r="W156" s="5"/>
       <c r="X156" s="5"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:24" ht="15.75" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4656,7 +4767,7 @@
       <c r="W157" s="5"/>
       <c r="X157" s="5"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:24" ht="15.75" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4682,7 +4793,7 @@
       <c r="W158" s="5"/>
       <c r="X158" s="5"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:24" ht="15.75" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4708,7 +4819,7 @@
       <c r="W159" s="5"/>
       <c r="X159" s="5"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:24" ht="15.75" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4734,7 +4845,7 @@
       <c r="W160" s="5"/>
       <c r="X160" s="5"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:24" ht="15.75" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4760,7 +4871,7 @@
       <c r="W161" s="5"/>
       <c r="X161" s="5"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:24" ht="15.75" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4786,7 +4897,7 @@
       <c r="W162" s="5"/>
       <c r="X162" s="5"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:24" ht="15.75" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4812,7 +4923,7 @@
       <c r="W163" s="5"/>
       <c r="X163" s="5"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:24" ht="15.75" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4838,7 +4949,7 @@
       <c r="W164" s="5"/>
       <c r="X164" s="5"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:24" ht="15.75" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4864,7 +4975,7 @@
       <c r="W165" s="5"/>
       <c r="X165" s="5"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:24" ht="15.75" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4890,7 +5001,7 @@
       <c r="W166" s="5"/>
       <c r="X166" s="5"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:24" ht="15.75" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4916,7 +5027,7 @@
       <c r="W167" s="5"/>
       <c r="X167" s="5"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:24" ht="15.75" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4942,7 +5053,7 @@
       <c r="W168" s="5"/>
       <c r="X168" s="5"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:24" ht="15.75" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4968,7 +5079,7 @@
       <c r="W169" s="5"/>
       <c r="X169" s="5"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:24" ht="15.75" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -4994,7 +5105,7 @@
       <c r="W170" s="5"/>
       <c r="X170" s="5"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:24" ht="15.75" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5020,7 +5131,7 @@
       <c r="W171" s="5"/>
       <c r="X171" s="5"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:24" ht="15.75" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5046,7 +5157,7 @@
       <c r="W172" s="5"/>
       <c r="X172" s="5"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:24" ht="15.75" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5072,7 +5183,7 @@
       <c r="W173" s="5"/>
       <c r="X173" s="5"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:24" ht="15.75" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5098,7 +5209,7 @@
       <c r="W174" s="5"/>
       <c r="X174" s="5"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:24" ht="15.75" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5124,7 +5235,7 @@
       <c r="W175" s="5"/>
       <c r="X175" s="5"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:24" ht="15.75" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5150,7 +5261,7 @@
       <c r="W176" s="5"/>
       <c r="X176" s="5"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:24" ht="15.75" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5176,7 +5287,7 @@
       <c r="W177" s="5"/>
       <c r="X177" s="5"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:24" ht="15.75" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5202,7 +5313,7 @@
       <c r="W178" s="5"/>
       <c r="X178" s="5"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:24" ht="15.75" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5228,7 +5339,7 @@
       <c r="W179" s="5"/>
       <c r="X179" s="5"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:24" ht="15.75" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5254,7 +5365,7 @@
       <c r="W180" s="5"/>
       <c r="X180" s="5"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:24" ht="15.75" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5280,7 +5391,7 @@
       <c r="W181" s="5"/>
       <c r="X181" s="5"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:24" ht="15.75" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5306,7 +5417,7 @@
       <c r="W182" s="5"/>
       <c r="X182" s="5"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:24" ht="15.75" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5332,7 +5443,7 @@
       <c r="W183" s="5"/>
       <c r="X183" s="5"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:24" ht="15.75" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5358,7 +5469,7 @@
       <c r="W184" s="5"/>
       <c r="X184" s="5"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:24" ht="15.75" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5384,7 +5495,7 @@
       <c r="W185" s="5"/>
       <c r="X185" s="5"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:24" ht="15.75" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5410,7 +5521,7 @@
       <c r="W186" s="5"/>
       <c r="X186" s="5"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:24" ht="15.75" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5436,7 +5547,7 @@
       <c r="W187" s="5"/>
       <c r="X187" s="5"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:24" ht="15.75" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5462,7 +5573,7 @@
       <c r="W188" s="5"/>
       <c r="X188" s="5"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:24" ht="15.75" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5488,7 +5599,7 @@
       <c r="W189" s="5"/>
       <c r="X189" s="5"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:24" ht="15.75" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5514,7 +5625,7 @@
       <c r="W190" s="5"/>
       <c r="X190" s="5"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:24" ht="15.75" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5540,7 +5651,7 @@
       <c r="W191" s="5"/>
       <c r="X191" s="5"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:24" ht="15.75" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5566,7 +5677,7 @@
       <c r="W192" s="5"/>
       <c r="X192" s="5"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:24" ht="15.75" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5592,7 +5703,7 @@
       <c r="W193" s="5"/>
       <c r="X193" s="5"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:24" ht="15.75" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5618,7 +5729,7 @@
       <c r="W194" s="5"/>
       <c r="X194" s="5"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:24" ht="15.75" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5644,7 +5755,7 @@
       <c r="W195" s="5"/>
       <c r="X195" s="5"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:24" ht="15.75" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5670,7 +5781,7 @@
       <c r="W196" s="5"/>
       <c r="X196" s="5"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:24" ht="15.75" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5696,7 +5807,7 @@
       <c r="W197" s="5"/>
       <c r="X197" s="5"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:24" ht="15.75" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5722,7 +5833,7 @@
       <c r="W198" s="5"/>
       <c r="X198" s="5"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:24" ht="15.75" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5748,7 +5859,7 @@
       <c r="W199" s="5"/>
       <c r="X199" s="5"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:24" ht="15.75" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5774,7 +5885,7 @@
       <c r="W200" s="5"/>
       <c r="X200" s="5"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:24" ht="15.75" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5800,7 +5911,7 @@
       <c r="W201" s="5"/>
       <c r="X201" s="5"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:24" ht="15.75" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5826,7 +5937,7 @@
       <c r="W202" s="5"/>
       <c r="X202" s="5"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:24" ht="15.75" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5852,7 +5963,7 @@
       <c r="W203" s="5"/>
       <c r="X203" s="5"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:24" ht="15.75" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5878,7 +5989,7 @@
       <c r="W204" s="5"/>
       <c r="X204" s="5"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:24" ht="15.75" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5904,7 +6015,7 @@
       <c r="W205" s="5"/>
       <c r="X205" s="5"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:24" ht="15.75" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5930,7 +6041,7 @@
       <c r="W206" s="5"/>
       <c r="X206" s="5"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:24" ht="15.75" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5956,7 +6067,7 @@
       <c r="W207" s="5"/>
       <c r="X207" s="5"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:24" ht="15.75" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5982,7 +6093,7 @@
       <c r="W208" s="5"/>
       <c r="X208" s="5"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:24" ht="15.75" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -6008,7 +6119,7 @@
       <c r="W209" s="5"/>
       <c r="X209" s="5"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:24" ht="15.75" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -6034,7 +6145,7 @@
       <c r="W210" s="5"/>
       <c r="X210" s="5"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:24" ht="15.75" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -6060,7 +6171,7 @@
       <c r="W211" s="5"/>
       <c r="X211" s="5"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:24" ht="15.75" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -6086,7 +6197,7 @@
       <c r="W212" s="5"/>
       <c r="X212" s="5"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:24" ht="15.75" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -6112,7 +6223,7 @@
       <c r="W213" s="5"/>
       <c r="X213" s="5"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:24" ht="15.75" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -6138,7 +6249,7 @@
       <c r="W214" s="5"/>
       <c r="X214" s="5"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:24" ht="15.75" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -6164,7 +6275,7 @@
       <c r="W215" s="5"/>
       <c r="X215" s="5"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:24" ht="15.75" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -6190,7 +6301,7 @@
       <c r="W216" s="5"/>
       <c r="X216" s="5"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:24" ht="15.75" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -6216,7 +6327,7 @@
       <c r="W217" s="5"/>
       <c r="X217" s="5"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:24" ht="15.75" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -6242,7 +6353,7 @@
       <c r="W218" s="5"/>
       <c r="X218" s="5"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:24" ht="15.75" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -6268,7 +6379,7 @@
       <c r="W219" s="5"/>
       <c r="X219" s="5"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:24" ht="15.75" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -6294,10 +6405,10 @@
       <c r="W220" s="5"/>
       <c r="X220" s="5"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:24" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:24" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -7075,9 +7186,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PetData.xlsx
+++ b/JsonConverter/ExcelFiles/PetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>아이디</t>
   </si>
@@ -121,6 +121,12 @@
     <t>pet_skill_fire_001</t>
   </si>
   <si>
+    <t>pet_passive_fire_force</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Fire_001</t>
+  </si>
+  <si>
     <t>pet_water_002</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>pet_passive_water_regeneration</t>
   </si>
   <si>
+    <t>Sprites/UI/Icon/PetIcon_Water_001</t>
+  </si>
+  <si>
     <t>pet_earth_003</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
     <t>pet_skill_earth_001,pet_skill_taunt</t>
   </si>
   <si>
+    <t>Sprites/UI/Icon/PetIcon_Earth_001</t>
+  </si>
+  <si>
     <t>pet_air_004</t>
   </si>
   <si>
@@ -167,6 +179,9 @@
   </si>
   <si>
     <t>pet_skill_air_001,pet_skill_windblessing</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/PetIcon_Air_001</t>
   </si>
 </sst>
 </file>
@@ -231,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -249,6 +264,12 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +495,8 @@
     <col customWidth="1" min="5" max="5" width="16.0"/>
     <col customWidth="1" min="6" max="6" width="28.0"/>
     <col customWidth="1" min="7" max="7" width="27.63"/>
-    <col customWidth="1" min="8" max="24" width="13.0"/>
+    <col customWidth="1" min="8" max="8" width="34.88"/>
+    <col customWidth="1" min="9" max="24" width="13.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
@@ -622,8 +644,12 @@
       <c r="F4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -643,27 +669,29 @@
     </row>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -683,25 +711,27 @@
     </row>
     <row r="6" ht="31.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -721,25 +751,27 @@
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
